--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run6/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run6/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.1606,0.7979,0.0624,0.1290</t>
-  </si>
-  <si>
-    <t>0.0197,0.0152,0.0079,0.9823</t>
-  </si>
-  <si>
-    <t>0.7825,0.1063,0.0051,0.0983</t>
-  </si>
-  <si>
-    <t>0.3560,0.0113,0.0068,0.7341</t>
-  </si>
-  <si>
-    <t>0.9884,0.0045,0.0015,0.0043</t>
-  </si>
-  <si>
-    <t>0.9795,0.0098,0.0019,0.0069</t>
-  </si>
-  <si>
-    <t>0.9801,0.0145,0.0022,0.0042</t>
-  </si>
-  <si>
-    <t>0.9738,0.0196,0.0026,0.0058</t>
-  </si>
-  <si>
-    <t>0.9703,0.0247,0.0029,0.0047</t>
-  </si>
-  <si>
-    <t>0.9770,0.0153,0.0020,0.0053</t>
-  </si>
-  <si>
-    <t>0.9778,0.0106,0.0016,0.0083</t>
-  </si>
-  <si>
-    <t>0.9779,0.0108,0.0023,0.0073</t>
-  </si>
-  <si>
-    <t>0.1450,0.7082,0.2033,0.0213</t>
-  </si>
-  <si>
-    <t>0.3622,0.1799,0.4634,0.0194</t>
-  </si>
-  <si>
-    <t>0.2443,0.2572,0.4574,0.0100</t>
-  </si>
-  <si>
-    <t>0.1646,0.6922,0.2296,0.0413</t>
-  </si>
-  <si>
-    <t>0.4109,0.2979,0.2797,0.0305</t>
-  </si>
-  <si>
-    <t>0.0032,0.9919,0.0220,0.0005</t>
-  </si>
-  <si>
-    <t>0.0042,0.9901,0.0253,0.0006</t>
-  </si>
-  <si>
-    <t>0.0333,0.9621,0.0167,0.0045</t>
-  </si>
-  <si>
-    <t>0.0086,0.9834,0.0197,0.0013</t>
-  </si>
-  <si>
-    <t>0.0007,0.9975,0.0105,0.0004</t>
-  </si>
-  <si>
-    <t>0.6778,0.0950,0.2363,0.0788</t>
-  </si>
-  <si>
-    <t>0.4469,0.0338,0.5992,0.0169</t>
-  </si>
-  <si>
-    <t>0.0345,0.0068,0.9678,0.0065</t>
-  </si>
-  <si>
-    <t>0.3118,0.0874,0.6555,0.0434</t>
-  </si>
-  <si>
-    <t>0.2173,0.0189,0.8538,0.0094</t>
-  </si>
-  <si>
-    <t>0.0956,0.0189,0.9121,0.0077</t>
-  </si>
-  <si>
-    <t>0.0058,0.0026,0.9763,0.0441</t>
-  </si>
-  <si>
-    <t>0.0952,0.9019,0.0397,0.0115</t>
-  </si>
-  <si>
-    <t>0.1516,0.7721,0.1262,0.0137</t>
-  </si>
-  <si>
-    <t>0.0172,0.0452,0.9696,0.0211</t>
-  </si>
-  <si>
-    <t>0.0131,0.9480,0.1200,0.0013</t>
-  </si>
-  <si>
-    <t>0.4773,0.5469,0.0534,0.0551</t>
-  </si>
-  <si>
-    <t>0.5077,0.4162,0.1235,0.0335</t>
-  </si>
-  <si>
-    <t>0.4476,0.5781,0.0504,0.0082</t>
-  </si>
-  <si>
-    <t>0.0299,0.9215,0.1270,0.0022</t>
-  </si>
-  <si>
-    <t>0.0204,0.9552,0.0685,0.0277</t>
-  </si>
-  <si>
-    <t>0.2142,0.3680,0.5549,0.0478</t>
-  </si>
-  <si>
-    <t>0.1668,0.2388,0.7143,0.0247</t>
-  </si>
-  <si>
-    <t>0.0410,0.5921,0.7806,0.0121</t>
-  </si>
-  <si>
-    <t>0.0156,0.7317,0.8329,0.0049</t>
-  </si>
-  <si>
-    <t>0.0234,0.9385,0.1225,0.0191</t>
-  </si>
-  <si>
-    <t>0.0917,0.0386,0.9155,0.0045</t>
-  </si>
-  <si>
-    <t>0.0843,0.7557,0.0880,0.4382</t>
-  </si>
-  <si>
-    <t>0.0024,0.9937,0.0118,0.0031</t>
-  </si>
-  <si>
-    <t>0.0067,0.9803,0.0444,0.0013</t>
-  </si>
-  <si>
-    <t>0.0050,0.9861,0.0319,0.0015</t>
-  </si>
-  <si>
-    <t>0.0378,0.8638,0.4294,0.0641</t>
-  </si>
-  <si>
-    <t>0.0127,0.2091,0.9703,0.0067</t>
-  </si>
-  <si>
-    <t>0.3296,0.0569,0.6964,0.0219</t>
-  </si>
-  <si>
-    <t>0.0255,0.0060,0.9701,0.0106</t>
-  </si>
-  <si>
-    <t>0.0266,0.0912,0.9522,0.0153</t>
-  </si>
-  <si>
-    <t>0.0509,0.6425,0.6367,0.0153</t>
-  </si>
-  <si>
-    <t>0.5585,0.5105,0.0302,0.0088</t>
-  </si>
-  <si>
-    <t>0.9668,0.0186,0.0050,0.0107</t>
-  </si>
-  <si>
-    <t>0.9429,0.0414,0.0103,0.0137</t>
-  </si>
-  <si>
-    <t>0.1183,0.1218,0.8601,0.0202</t>
-  </si>
-  <si>
-    <t>0.9768,0.0166,0.0032,0.0043</t>
-  </si>
-  <si>
-    <t>0.9794,0.0127,0.0021,0.0054</t>
-  </si>
-  <si>
-    <t>0.9505,0.0428,0.0060,0.0075</t>
-  </si>
-  <si>
-    <t>0.0036,0.9717,0.5823,0.0027</t>
-  </si>
-  <si>
-    <t>0.0187,0.3331,0.9537,0.0151</t>
-  </si>
-  <si>
-    <t>0.1935,0.2016,0.6780,0.1158</t>
-  </si>
-  <si>
-    <t>0.0036,0.9788,0.3705,0.0072</t>
-  </si>
-  <si>
-    <t>0.0063,0.0157,0.9715,0.0346</t>
-  </si>
-  <si>
-    <t>0.0088,0.9712,0.1004,0.0009</t>
-  </si>
-  <si>
-    <t>0.0006,0.9986,0.0024,0.0008</t>
-  </si>
-  <si>
-    <t>0.7311,0.1536,0.1497,0.0703</t>
-  </si>
-  <si>
-    <t>0.1868,0.6943,0.1705,0.0189</t>
-  </si>
-  <si>
-    <t>0.0545,0.1994,0.8771,0.0210</t>
-  </si>
-  <si>
-    <t>0.0037,0.9630,0.6089,0.0008</t>
-  </si>
-  <si>
-    <t>0.0039,0.9665,0.4552,0.0011</t>
-  </si>
-  <si>
-    <t>0.0034,0.9877,0.0834,0.0026</t>
-  </si>
-  <si>
-    <t>0.0076,0.9748,0.1920,0.0079</t>
-  </si>
-  <si>
-    <t>0.0875,0.0127,0.0111,0.9269</t>
-  </si>
-  <si>
-    <t>0.0114,0.0572,0.0055,0.9861</t>
-  </si>
-  <si>
-    <t>0.0102,0.0536,0.0039,0.9885</t>
-  </si>
-  <si>
-    <t>0.0146,0.0980,0.0072,0.9803</t>
-  </si>
-  <si>
-    <t>0.0856,0.0137,0.0130,0.9284</t>
-  </si>
-  <si>
-    <t>0.0082,0.0348,0.0032,0.9900</t>
-  </si>
-  <si>
-    <t>0.0042,0.9827,0.1729,0.0041</t>
-  </si>
-  <si>
-    <t>0.0044,0.9802,0.3193,0.0018</t>
-  </si>
-  <si>
-    <t>0.0094,0.9535,0.2990,0.0031</t>
-  </si>
-  <si>
-    <t>0.0176,0.8907,0.6315,0.0063</t>
-  </si>
-  <si>
-    <t>0.0035,0.9862,0.2146,0.0008</t>
-  </si>
-  <si>
-    <t>0.0182,0.9034,0.5723,0.0153</t>
-  </si>
-  <si>
-    <t>0.9663,0.0249,0.0040,0.0073</t>
-  </si>
-  <si>
-    <t>0.7766,0.2570,0.0186,0.0097</t>
-  </si>
-  <si>
-    <t>0.9171,0.0785,0.0096,0.0082</t>
-  </si>
-  <si>
-    <t>0.9520,0.0324,0.0035,0.0097</t>
-  </si>
-  <si>
-    <t>0.9787,0.0146,0.0034,0.0036</t>
-  </si>
-  <si>
-    <t>0.9814,0.0130,0.0019,0.0039</t>
-  </si>
-  <si>
-    <t>0.9581,0.0334,0.0052,0.0093</t>
-  </si>
-  <si>
-    <t>0.8800,0.1421,0.0085,0.0090</t>
-  </si>
-  <si>
-    <t>0.9842,0.0071,0.0016,0.0061</t>
-  </si>
-  <si>
-    <t>0.9526,0.0365,0.0053,0.0080</t>
-  </si>
-  <si>
-    <t>0.9901,0.0062,0.0009,0.0024</t>
-  </si>
-  <si>
-    <t>0.9922,0.0027,0.0007,0.0032</t>
-  </si>
-  <si>
-    <t>0.9807,0.0101,0.0024,0.0050</t>
-  </si>
-  <si>
-    <t>0.9829,0.0108,0.0016,0.0041</t>
-  </si>
-  <si>
-    <t>0.9825,0.0099,0.0013,0.0053</t>
-  </si>
-  <si>
-    <t>0.9872,0.0044,0.0011,0.0059</t>
-  </si>
-  <si>
-    <t>0.0022,0.0024,0.9961,0.0032</t>
-  </si>
-  <si>
-    <t>0.0806,0.5763,0.6221,0.0216</t>
-  </si>
-  <si>
-    <t>0.6191,0.1549,0.2529,0.0552</t>
-  </si>
-  <si>
-    <t>0.0281,0.0152,0.9721,0.0067</t>
-  </si>
-  <si>
-    <t>0.0060,0.9866,0.0146,0.0028</t>
-  </si>
-  <si>
-    <t>0.0076,0.9861,0.0136,0.0021</t>
-  </si>
-  <si>
-    <t>0.0252,0.9557,0.0368,0.0044</t>
-  </si>
-  <si>
-    <t>0.0312,0.9426,0.0555,0.0028</t>
-  </si>
-  <si>
-    <t>0.0036,0.9896,0.0245,0.0009</t>
-  </si>
-  <si>
-    <t>0.0022,0.9944,0.0089,0.0007</t>
-  </si>
-  <si>
-    <t>0.0802,0.9251,0.0201,0.0058</t>
-  </si>
-  <si>
-    <t>0.2246,0.5047,0.2902,0.0327</t>
-  </si>
-  <si>
-    <t>0.1776,0.2175,0.6499,0.0128</t>
-  </si>
-  <si>
-    <t>0.5261,0.1766,0.2268,0.0161</t>
-  </si>
-  <si>
-    <t>0.4762,0.2947,0.2011,0.0333</t>
-  </si>
-  <si>
-    <t>0.1055,0.1113,0.0813,0.8337</t>
-  </si>
-  <si>
-    <t>0.0021,0.9944,0.0124,0.0009</t>
-  </si>
-  <si>
-    <t>0.0017,0.9950,0.0101,0.0031</t>
-  </si>
-  <si>
-    <t>0.0165,0.9634,0.0724,0.0125</t>
-  </si>
-  <si>
-    <t>0.0007,0.9979,0.0165,0.0007</t>
-  </si>
-  <si>
-    <t>0.0297,0.9375,0.0741,0.0018</t>
-  </si>
-  <si>
-    <t>0.3955,0.6392,0.0456,0.0074</t>
-  </si>
-  <si>
-    <t>0.1076,0.8730,0.0538,0.0032</t>
-  </si>
-  <si>
-    <t>0.7455,0.2700,0.0255,0.0205</t>
-  </si>
-  <si>
-    <t>0.9683,0.0150,0.0043,0.0103</t>
-  </si>
-  <si>
-    <t>0.9800,0.0066,0.0017,0.0096</t>
-  </si>
-  <si>
-    <t>0.9607,0.0176,0.0023,0.0167</t>
-  </si>
-  <si>
-    <t>0.9746,0.0106,0.0024,0.0117</t>
-  </si>
-  <si>
-    <t>0.9641,0.0299,0.0050,0.0055</t>
-  </si>
-  <si>
-    <t>0.9672,0.0186,0.0025,0.0110</t>
-  </si>
-  <si>
-    <t>0.9773,0.0124,0.0030,0.0067</t>
-  </si>
-  <si>
-    <t>0.0155,0.8808,0.7705,0.0066</t>
-  </si>
-  <si>
-    <t>0.0084,0.9186,0.6913,0.0021</t>
-  </si>
-  <si>
-    <t>0.0357,0.5229,0.7329,0.0078</t>
-  </si>
-  <si>
-    <t>0.0532,0.7565,0.5534,0.0087</t>
-  </si>
-  <si>
-    <t>0.8324,0.0493,0.1074,0.0135</t>
-  </si>
-  <si>
-    <t>0.7478,0.0967,0.1530,0.0200</t>
-  </si>
-  <si>
-    <t>0.4109,0.0327,0.6747,0.0220</t>
-  </si>
-  <si>
-    <t>0.3842,0.3594,0.2480,0.0488</t>
-  </si>
-  <si>
-    <t>0.0292,0.0246,0.0062,0.9762</t>
-  </si>
-  <si>
-    <t>0.0007,0.0028,0.0018,0.9987</t>
-  </si>
-  <si>
-    <t>0.0031,0.0509,0.0023,0.9950</t>
-  </si>
-  <si>
-    <t>0.0281,0.0387,0.0060,0.9746</t>
-  </si>
-  <si>
-    <t>0.0131,0.9549,0.2342,0.0142</t>
-  </si>
-  <si>
-    <t>0.9369,0.0490,0.0097,0.0130</t>
-  </si>
-  <si>
-    <t>0.1344,0.8661,0.0199,0.0337</t>
-  </si>
-  <si>
-    <t>0.9280,0.0455,0.0117,0.0219</t>
-  </si>
-  <si>
-    <t>0.1306,0.8603,0.0442,0.0101</t>
-  </si>
-  <si>
-    <t>0.9666,0.0180,0.0047,0.0088</t>
-  </si>
-  <si>
-    <t>0.7926,0.0309,0.0559,0.1637</t>
-  </si>
-  <si>
-    <t>0.9494,0.0123,0.0035,0.0358</t>
-  </si>
-  <si>
-    <t>0.3463,0.2431,0.2389,0.4290</t>
-  </si>
-  <si>
-    <t>0.8311,0.0095,0.0190,0.1664</t>
-  </si>
-  <si>
-    <t>0.9409,0.0156,0.0139,0.0333</t>
-  </si>
-  <si>
-    <t>0.4205,0.5903,0.0645,0.0281</t>
-  </si>
-  <si>
-    <t>0.6793,0.2936,0.0517,0.0540</t>
-  </si>
-  <si>
-    <t>0.1280,0.8302,0.1062,0.0373</t>
-  </si>
-  <si>
-    <t>0.1035,0.8683,0.0458,0.0331</t>
-  </si>
-  <si>
-    <t>0.2802,0.6503,0.1092,0.0251</t>
-  </si>
-  <si>
-    <t>0.6012,0.3550,0.0745,0.0256</t>
-  </si>
-  <si>
-    <t>0.9486,0.0279,0.0091,0.0149</t>
-  </si>
-  <si>
-    <t>0.9330,0.0534,0.0089,0.0125</t>
-  </si>
-  <si>
-    <t>0.9514,0.0290,0.0048,0.0158</t>
-  </si>
-  <si>
-    <t>0.9644,0.0177,0.0037,0.0154</t>
-  </si>
-  <si>
-    <t>0.9719,0.0168,0.0035,0.0067</t>
-  </si>
-  <si>
-    <t>0.9786,0.0125,0.0027,0.0051</t>
-  </si>
-  <si>
-    <t>0.9820,0.0087,0.0021,0.0063</t>
-  </si>
-  <si>
-    <t>0.9496,0.0171,0.0030,0.0281</t>
-  </si>
-  <si>
-    <t>0.0277,0.9566,0.0375,0.0035</t>
-  </si>
-  <si>
-    <t>0.1545,0.8473,0.0403,0.0069</t>
-  </si>
-  <si>
-    <t>0.0357,0.9562,0.0216,0.0039</t>
-  </si>
-  <si>
-    <t>0.0686,0.5406,0.6505,0.0067</t>
-  </si>
-  <si>
-    <t>0.8107,0.2244,0.0169,0.0097</t>
-  </si>
-  <si>
-    <t>0.4393,0.6414,0.0151,0.0255</t>
-  </si>
-  <si>
-    <t>0.9463,0.0453,0.0070,0.0088</t>
-  </si>
-  <si>
-    <t>0.3301,0.7233,0.0315,0.0161</t>
-  </si>
-  <si>
-    <t>0.0011,0.0111,0.9980,0.0013</t>
-  </si>
-  <si>
-    <t>0.8434,0.1626,0.0244,0.0079</t>
-  </si>
-  <si>
-    <t>0.0441,0.0119,0.9628,0.0051</t>
-  </si>
-  <si>
-    <t>0.0376,0.4387,0.8767,0.0137</t>
-  </si>
-  <si>
-    <t>0.1413,0.0143,0.9115,0.0065</t>
-  </si>
-  <si>
-    <t>0.0308,0.4460,0.9103,0.0118</t>
-  </si>
-  <si>
-    <t>0.1447,0.1837,0.7816,0.0397</t>
-  </si>
-  <si>
-    <t>0.0470,0.0129,0.9679,0.0032</t>
-  </si>
-  <si>
-    <t>0.1479,0.0746,0.8452,0.0240</t>
-  </si>
-  <si>
-    <t>0.1635,0.1351,0.7105,0.0110</t>
-  </si>
-  <si>
-    <t>0.2269,0.2376,0.5375,0.0249</t>
-  </si>
-  <si>
-    <t>0.3262,0.2863,0.4181,0.0291</t>
-  </si>
-  <si>
-    <t>0.0740,0.6142,0.4334,0.0101</t>
-  </si>
-  <si>
-    <t>0.0697,0.8720,0.1064,0.0389</t>
-  </si>
-  <si>
-    <t>0.3963,0.2309,0.2965,0.0093</t>
-  </si>
-  <si>
-    <t>0.2536,0.6452,0.1906,0.0608</t>
-  </si>
-  <si>
-    <t>0.6199,0.1315,0.2847,0.0423</t>
-  </si>
-  <si>
-    <t>0.1701,0.8467,0.0291,0.0045</t>
-  </si>
-  <si>
-    <t>0.1596,0.8528,0.0313,0.0053</t>
-  </si>
-  <si>
-    <t>0.1188,0.8801,0.0430,0.0047</t>
-  </si>
-  <si>
-    <t>0.4968,0.6154,0.0186,0.0048</t>
-  </si>
-  <si>
-    <t>0.2036,0.8429,0.0207,0.0058</t>
-  </si>
-  <si>
-    <t>0.1688,0.7594,0.1199,0.0328</t>
-  </si>
-  <si>
-    <t>0.7000,0.1154,0.2156,0.0259</t>
-  </si>
-  <si>
-    <t>0.6093,0.1307,0.2463,0.0267</t>
-  </si>
-  <si>
-    <t>0.6591,0.0638,0.3455,0.0256</t>
-  </si>
-  <si>
-    <t>0.7695,0.0704,0.1888,0.0315</t>
-  </si>
-  <si>
-    <t>0.2572,0.1036,0.7054,0.0651</t>
-  </si>
-  <si>
-    <t>0.0631,0.6868,0.6684,0.0346</t>
-  </si>
-  <si>
-    <t>0.1598,0.2192,0.7128,0.0978</t>
-  </si>
-  <si>
-    <t>0.0940,0.3255,0.7194,0.0100</t>
-  </si>
-  <si>
-    <t>0.0809,0.4217,0.7024,0.0314</t>
-  </si>
-  <si>
-    <t>0.9567,0.0246,0.0031,0.0129</t>
-  </si>
-  <si>
-    <t>0.9837,0.0091,0.0025,0.0039</t>
-  </si>
-  <si>
-    <t>0.9530,0.0266,0.0027,0.0134</t>
-  </si>
-  <si>
-    <t>0.9771,0.0170,0.0034,0.0037</t>
-  </si>
-  <si>
-    <t>0.9278,0.0668,0.0067,0.0081</t>
-  </si>
-  <si>
-    <t>0.9708,0.0206,0.0037,0.0069</t>
-  </si>
-  <si>
-    <t>0.9855,0.0057,0.0018,0.0057</t>
-  </si>
-  <si>
-    <t>0.8881,0.1161,0.0129,0.0108</t>
-  </si>
-  <si>
-    <t>0.1608,0.1977,0.7154,0.0080</t>
-  </si>
-  <si>
-    <t>0.1446,0.7317,0.1909,0.0147</t>
-  </si>
-  <si>
-    <t>0.6493,0.2484,0.0545,0.1313</t>
-  </si>
-  <si>
-    <t>0.0533,0.0768,0.9251,0.0186</t>
-  </si>
-  <si>
-    <t>0.0456,0.1057,0.8873,0.0675</t>
-  </si>
-  <si>
-    <t>0.0896,0.2268,0.7876,0.0228</t>
-  </si>
-  <si>
-    <t>0.0034,0.0093,0.9910,0.0072</t>
-  </si>
-  <si>
-    <t>0.1055,0.1650,0.7831,0.0201</t>
-  </si>
-  <si>
-    <t>0.0317,0.0395,0.9605,0.0155</t>
-  </si>
-  <si>
-    <t>0.0912,0.1286,0.8100,0.0677</t>
-  </si>
-  <si>
-    <t>0.0891,0.6357,0.4770,0.0195</t>
-  </si>
-  <si>
-    <t>0.7761,0.0279,0.2650,0.0123</t>
-  </si>
-  <si>
-    <t>0.5883,0.0958,0.3845,0.0608</t>
-  </si>
-  <si>
-    <t>0.8015,0.0376,0.1966,0.0119</t>
-  </si>
-  <si>
-    <t>0.8436,0.1629,0.0091,0.0135</t>
-  </si>
-  <si>
-    <t>0.9822,0.0124,0.0017,0.0040</t>
-  </si>
-  <si>
-    <t>0.9789,0.0091,0.0016,0.0086</t>
-  </si>
-  <si>
-    <t>0.9610,0.0295,0.0065,0.0069</t>
-  </si>
-  <si>
-    <t>0.9865,0.0083,0.0013,0.0033</t>
-  </si>
-  <si>
-    <t>0.9748,0.0189,0.0024,0.0044</t>
-  </si>
-  <si>
-    <t>0.9110,0.0898,0.0077,0.0089</t>
-  </si>
-  <si>
-    <t>0.9674,0.0196,0.0035,0.0109</t>
-  </si>
-  <si>
-    <t>0.1583,0.2548,0.6246,0.0142</t>
-  </si>
-  <si>
-    <t>0.0296,0.0864,0.9333,0.0251</t>
-  </si>
-  <si>
-    <t>0.0692,0.2314,0.8425,0.0601</t>
-  </si>
-  <si>
-    <t>0.1565,0.2885,0.5496,0.0129</t>
-  </si>
-  <si>
-    <t>0.0923,0.0167,0.9026,0.0276</t>
-  </si>
-  <si>
-    <t>0.0765,0.0678,0.8121,0.1862</t>
-  </si>
-  <si>
-    <t>0.4239,0.0397,0.6551,0.0181</t>
-  </si>
-  <si>
-    <t>0.2314,0.1331,0.6346,0.1410</t>
-  </si>
-  <si>
-    <t>0.6895,0.0317,0.0085,0.3584</t>
-  </si>
-  <si>
-    <t>0.0510,0.0613,0.0242,0.9478</t>
-  </si>
-  <si>
-    <t>0.0132,0.0543,0.0033,0.9858</t>
-  </si>
-  <si>
-    <t>0.0034,0.0051,0.0021,0.9961</t>
-  </si>
-  <si>
-    <t>0.0032,0.0149,0.0015,0.9965</t>
-  </si>
-  <si>
-    <t>0.4299,0.1306,0.1118,0.5187</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.5368,0.2206,0.0667,0.3390</t>
+  </si>
+  <si>
+    <t>0.1431,0.0487,0.0217,0.8865</t>
+  </si>
+  <si>
+    <t>0.5210,0.2851,0.0050,0.1653</t>
+  </si>
+  <si>
+    <t>0.2034,0.0138,0.0143,0.8514</t>
+  </si>
+  <si>
+    <t>0.9808,0.0104,0.0036,0.0057</t>
+  </si>
+  <si>
+    <t>0.9796,0.0093,0.0022,0.0069</t>
+  </si>
+  <si>
+    <t>0.9727,0.0197,0.0036,0.0054</t>
+  </si>
+  <si>
+    <t>0.9697,0.0186,0.0037,0.0092</t>
+  </si>
+  <si>
+    <t>0.9600,0.0326,0.0027,0.0073</t>
+  </si>
+  <si>
+    <t>0.9763,0.0202,0.0019,0.0035</t>
+  </si>
+  <si>
+    <t>0.9853,0.0070,0.0011,0.0050</t>
+  </si>
+  <si>
+    <t>0.9781,0.0095,0.0024,0.0088</t>
+  </si>
+  <si>
+    <t>0.4555,0.3885,0.1344,0.0178</t>
+  </si>
+  <si>
+    <t>0.0887,0.1847,0.8153,0.0120</t>
+  </si>
+  <si>
+    <t>0.2010,0.2262,0.5643,0.0099</t>
+  </si>
+  <si>
+    <t>0.3451,0.2448,0.3704,0.0338</t>
+  </si>
+  <si>
+    <t>0.4392,0.1882,0.4653,0.0568</t>
+  </si>
+  <si>
+    <t>0.0062,0.9851,0.0265,0.0018</t>
+  </si>
+  <si>
+    <t>0.0028,0.9925,0.0179,0.0007</t>
+  </si>
+  <si>
+    <t>0.1176,0.8848,0.0367,0.0090</t>
+  </si>
+  <si>
+    <t>0.0047,0.9874,0.0279,0.0007</t>
+  </si>
+  <si>
+    <t>0.0017,0.9941,0.0231,0.0004</t>
+  </si>
+  <si>
+    <t>0.6919,0.0801,0.2600,0.0668</t>
+  </si>
+  <si>
+    <t>0.5168,0.0492,0.5036,0.0323</t>
+  </si>
+  <si>
+    <t>0.0268,0.0051,0.9769,0.0050</t>
+  </si>
+  <si>
+    <t>0.2603,0.0856,0.6847,0.0389</t>
+  </si>
+  <si>
+    <t>0.1353,0.0328,0.8805,0.0125</t>
+  </si>
+  <si>
+    <t>0.2543,0.0633,0.7347,0.0407</t>
+  </si>
+  <si>
+    <t>0.0713,0.0156,0.9077,0.0362</t>
+  </si>
+  <si>
+    <t>0.0292,0.9528,0.0347,0.0065</t>
+  </si>
+  <si>
+    <t>0.1340,0.7616,0.1559,0.0092</t>
+  </si>
+  <si>
+    <t>0.0583,0.0456,0.9069,0.0732</t>
+  </si>
+  <si>
+    <t>0.0065,0.9728,0.0887,0.0009</t>
+  </si>
+  <si>
+    <t>0.5330,0.4716,0.0446,0.0367</t>
+  </si>
+  <si>
+    <t>0.6950,0.2786,0.0700,0.0439</t>
+  </si>
+  <si>
+    <t>0.2323,0.7332,0.0699,0.0073</t>
+  </si>
+  <si>
+    <t>0.0070,0.9743,0.1156,0.0006</t>
+  </si>
+  <si>
+    <t>0.0300,0.9454,0.0321,0.0620</t>
+  </si>
+  <si>
+    <t>0.1938,0.5553,0.4141,0.1362</t>
+  </si>
+  <si>
+    <t>0.1125,0.6789,0.4932,0.0375</t>
+  </si>
+  <si>
+    <t>0.2470,0.0301,0.7953,0.0201</t>
+  </si>
+  <si>
+    <t>0.0233,0.8275,0.6407,0.0065</t>
+  </si>
+  <si>
+    <t>0.0096,0.9804,0.0304,0.0046</t>
+  </si>
+  <si>
+    <t>0.1156,0.3145,0.7496,0.0602</t>
+  </si>
+  <si>
+    <t>0.1220,0.7540,0.1221,0.2351</t>
+  </si>
+  <si>
+    <t>0.0046,0.9886,0.0178,0.0080</t>
+  </si>
+  <si>
+    <t>0.0035,0.9905,0.0184,0.0014</t>
+  </si>
+  <si>
+    <t>0.0025,0.9939,0.0123,0.0020</t>
+  </si>
+  <si>
+    <t>0.0466,0.7935,0.6343,0.0323</t>
+  </si>
+  <si>
+    <t>0.0245,0.7818,0.8212,0.0095</t>
+  </si>
+  <si>
+    <t>0.1859,0.0189,0.8509,0.0081</t>
+  </si>
+  <si>
+    <t>0.1394,0.0052,0.8877,0.0195</t>
+  </si>
+  <si>
+    <t>0.0286,0.0130,0.9478,0.0311</t>
+  </si>
+  <si>
+    <t>0.0649,0.0785,0.8972,0.0161</t>
+  </si>
+  <si>
+    <t>0.8810,0.1382,0.0151,0.0084</t>
+  </si>
+  <si>
+    <t>0.9792,0.0105,0.0040,0.0042</t>
+  </si>
+  <si>
+    <t>0.9567,0.0344,0.0054,0.0096</t>
+  </si>
+  <si>
+    <t>0.0308,0.2919,0.9134,0.0154</t>
+  </si>
+  <si>
+    <t>0.9680,0.0201,0.0055,0.0063</t>
+  </si>
+  <si>
+    <t>0.9700,0.0210,0.0032,0.0064</t>
+  </si>
+  <si>
+    <t>0.8625,0.1421,0.0128,0.0099</t>
+  </si>
+  <si>
+    <t>0.0025,0.9843,0.4363,0.0020</t>
+  </si>
+  <si>
+    <t>0.0756,0.4745,0.7937,0.0788</t>
+  </si>
+  <si>
+    <t>0.0569,0.4239,0.5458,0.2101</t>
+  </si>
+  <si>
+    <t>0.0096,0.9579,0.4187,0.0126</t>
+  </si>
+  <si>
+    <t>0.0031,0.0184,0.9842,0.0116</t>
+  </si>
+  <si>
+    <t>0.0060,0.9836,0.0490,0.0007</t>
+  </si>
+  <si>
+    <t>0.0011,0.9980,0.0041,0.0004</t>
+  </si>
+  <si>
+    <t>0.2111,0.0824,0.8058,0.0453</t>
+  </si>
+  <si>
+    <t>0.1257,0.6194,0.5139,0.0333</t>
+  </si>
+  <si>
+    <t>0.0325,0.5140,0.8660,0.0217</t>
+  </si>
+  <si>
+    <t>0.0095,0.9384,0.6089,0.0036</t>
+  </si>
+  <si>
+    <t>0.0045,0.9753,0.2476,0.0045</t>
+  </si>
+  <si>
+    <t>0.0044,0.9828,0.1487,0.0036</t>
+  </si>
+  <si>
+    <t>0.0065,0.9759,0.1903,0.0066</t>
+  </si>
+  <si>
+    <t>0.1038,0.0820,0.0169,0.8993</t>
+  </si>
+  <si>
+    <t>0.0168,0.0105,0.0041,0.9868</t>
+  </si>
+  <si>
+    <t>0.0107,0.0530,0.0044,0.9880</t>
+  </si>
+  <si>
+    <t>0.0569,0.0401,0.0101,0.9571</t>
+  </si>
+  <si>
+    <t>0.1925,0.0173,0.0119,0.8465</t>
+  </si>
+  <si>
+    <t>0.0136,0.0161,0.0049,0.9874</t>
+  </si>
+  <si>
+    <t>0.0085,0.9714,0.1664,0.0111</t>
+  </si>
+  <si>
+    <t>0.0048,0.9459,0.8417,0.0013</t>
+  </si>
+  <si>
+    <t>0.0061,0.9600,0.5572,0.0029</t>
+  </si>
+  <si>
+    <t>0.0096,0.8971,0.7585,0.0033</t>
+  </si>
+  <si>
+    <t>0.0093,0.9583,0.3930,0.0022</t>
+  </si>
+  <si>
+    <t>0.0149,0.9289,0.4947,0.0092</t>
+  </si>
+  <si>
+    <t>0.9646,0.0295,0.0036,0.0057</t>
+  </si>
+  <si>
+    <t>0.8316,0.1918,0.0155,0.0087</t>
+  </si>
+  <si>
+    <t>0.9191,0.0804,0.0047,0.0072</t>
+  </si>
+  <si>
+    <t>0.9539,0.0284,0.0046,0.0123</t>
+  </si>
+  <si>
+    <t>0.9744,0.0182,0.0039,0.0050</t>
+  </si>
+  <si>
+    <t>0.9830,0.0095,0.0019,0.0047</t>
+  </si>
+  <si>
+    <t>0.9535,0.0398,0.0054,0.0060</t>
+  </si>
+  <si>
+    <t>0.9621,0.0349,0.0044,0.0045</t>
+  </si>
+  <si>
+    <t>0.9748,0.0156,0.0032,0.0068</t>
+  </si>
+  <si>
+    <t>0.9701,0.0171,0.0037,0.0089</t>
+  </si>
+  <si>
+    <t>0.9791,0.0115,0.0015,0.0070</t>
+  </si>
+  <si>
+    <t>0.9884,0.0056,0.0014,0.0037</t>
+  </si>
+  <si>
+    <t>0.9838,0.0085,0.0016,0.0045</t>
+  </si>
+  <si>
+    <t>0.9522,0.0447,0.0060,0.0053</t>
+  </si>
+  <si>
+    <t>0.9762,0.0106,0.0018,0.0092</t>
+  </si>
+  <si>
+    <t>0.9856,0.0078,0.0018,0.0039</t>
+  </si>
+  <si>
+    <t>0.0076,0.0021,0.9923,0.0036</t>
+  </si>
+  <si>
+    <t>0.0538,0.4534,0.7988,0.0172</t>
+  </si>
+  <si>
+    <t>0.3708,0.4706,0.1347,0.0619</t>
+  </si>
+  <si>
+    <t>0.0410,0.0136,0.9471,0.0200</t>
+  </si>
+  <si>
+    <t>0.0057,0.9880,0.0136,0.0022</t>
+  </si>
+  <si>
+    <t>0.0071,0.9874,0.0111,0.0024</t>
+  </si>
+  <si>
+    <t>0.0256,0.9583,0.0325,0.0031</t>
+  </si>
+  <si>
+    <t>0.0469,0.9293,0.0491,0.0035</t>
+  </si>
+  <si>
+    <t>0.0054,0.9876,0.0181,0.0022</t>
+  </si>
+  <si>
+    <t>0.0027,0.9931,0.0137,0.0011</t>
+  </si>
+  <si>
+    <t>0.1799,0.8348,0.0344,0.0090</t>
+  </si>
+  <si>
+    <t>0.1835,0.6580,0.2544,0.0435</t>
+  </si>
+  <si>
+    <t>0.4178,0.0588,0.6082,0.0104</t>
+  </si>
+  <si>
+    <t>0.2577,0.5573,0.1690,0.0304</t>
+  </si>
+  <si>
+    <t>0.3338,0.4049,0.2999,0.0545</t>
+  </si>
+  <si>
+    <t>0.2017,0.4211,0.1241,0.5492</t>
+  </si>
+  <si>
+    <t>0.0013,0.9970,0.0055,0.0006</t>
+  </si>
+  <si>
+    <t>0.0010,0.9970,0.0049,0.0032</t>
+  </si>
+  <si>
+    <t>0.0138,0.9704,0.0285,0.0129</t>
+  </si>
+  <si>
+    <t>0.0009,0.9972,0.0180,0.0004</t>
+  </si>
+  <si>
+    <t>0.0059,0.9773,0.0968,0.0005</t>
+  </si>
+  <si>
+    <t>0.2614,0.7509,0.0509,0.0094</t>
+  </si>
+  <si>
+    <t>0.2130,0.7960,0.0470,0.0066</t>
+  </si>
+  <si>
+    <t>0.7847,0.2282,0.0214,0.0213</t>
+  </si>
+  <si>
+    <t>0.9682,0.0154,0.0045,0.0121</t>
+  </si>
+  <si>
+    <t>0.9681,0.0188,0.0040,0.0072</t>
+  </si>
+  <si>
+    <t>0.9562,0.0246,0.0054,0.0152</t>
+  </si>
+  <si>
+    <t>0.9618,0.0131,0.0015,0.0187</t>
+  </si>
+  <si>
+    <t>0.9533,0.0306,0.0116,0.0078</t>
+  </si>
+  <si>
+    <t>0.9355,0.0496,0.0080,0.0134</t>
+  </si>
+  <si>
+    <t>0.9433,0.0475,0.0047,0.0100</t>
+  </si>
+  <si>
+    <t>0.0505,0.6165,0.7697,0.0231</t>
+  </si>
+  <si>
+    <t>0.0155,0.9271,0.3976,0.0035</t>
+  </si>
+  <si>
+    <t>0.0171,0.2771,0.9161,0.0042</t>
+  </si>
+  <si>
+    <t>0.0442,0.5227,0.7418,0.0056</t>
+  </si>
+  <si>
+    <t>0.5160,0.3330,0.1502,0.0356</t>
+  </si>
+  <si>
+    <t>0.6175,0.1776,0.2679,0.0566</t>
+  </si>
+  <si>
+    <t>0.5649,0.0105,0.6614,0.0068</t>
+  </si>
+  <si>
+    <t>0.2183,0.7120,0.1132,0.0524</t>
+  </si>
+  <si>
+    <t>0.2284,0.0272,0.0070,0.8286</t>
+  </si>
+  <si>
+    <t>0.0010,0.0042,0.0032,0.9980</t>
+  </si>
+  <si>
+    <t>0.0088,0.0336,0.0075,0.9891</t>
+  </si>
+  <si>
+    <t>0.0211,0.0068,0.0039,0.9834</t>
+  </si>
+  <si>
+    <t>0.0059,0.9780,0.1195,0.0099</t>
+  </si>
+  <si>
+    <t>0.9262,0.0535,0.0095,0.0185</t>
+  </si>
+  <si>
+    <t>0.0906,0.8998,0.0189,0.0277</t>
+  </si>
+  <si>
+    <t>0.9554,0.0233,0.0057,0.0180</t>
+  </si>
+  <si>
+    <t>0.0365,0.9450,0.0373,0.0054</t>
+  </si>
+  <si>
+    <t>0.9154,0.0650,0.0056,0.0218</t>
+  </si>
+  <si>
+    <t>0.7737,0.0483,0.0611,0.1741</t>
+  </si>
+  <si>
+    <t>0.9733,0.0081,0.0079,0.0097</t>
+  </si>
+  <si>
+    <t>0.3379,0.4063,0.3507,0.0758</t>
+  </si>
+  <si>
+    <t>0.7589,0.0076,0.0311,0.2087</t>
+  </si>
+  <si>
+    <t>0.9310,0.0107,0.0077,0.0549</t>
+  </si>
+  <si>
+    <t>0.1702,0.8341,0.0323,0.0361</t>
+  </si>
+  <si>
+    <t>0.6373,0.3570,0.0560,0.0470</t>
+  </si>
+  <si>
+    <t>0.2043,0.7293,0.1140,0.0218</t>
+  </si>
+  <si>
+    <t>0.0888,0.8952,0.0345,0.0133</t>
+  </si>
+  <si>
+    <t>0.4345,0.4828,0.1166,0.0301</t>
+  </si>
+  <si>
+    <t>0.1440,0.7800,0.1198,0.0109</t>
+  </si>
+  <si>
+    <t>0.9706,0.0148,0.0025,0.0098</t>
+  </si>
+  <si>
+    <t>0.9646,0.0204,0.0020,0.0111</t>
+  </si>
+  <si>
+    <t>0.9782,0.0095,0.0025,0.0084</t>
+  </si>
+  <si>
+    <t>0.9492,0.0240,0.0077,0.0221</t>
+  </si>
+  <si>
+    <t>0.9578,0.0279,0.0051,0.0111</t>
+  </si>
+  <si>
+    <t>0.9820,0.0082,0.0033,0.0050</t>
+  </si>
+  <si>
+    <t>0.9688,0.0135,0.0027,0.0126</t>
+  </si>
+  <si>
+    <t>0.9733,0.0142,0.0029,0.0080</t>
+  </si>
+  <si>
+    <t>0.1333,0.8742,0.0321,0.0072</t>
+  </si>
+  <si>
+    <t>0.0661,0.9236,0.0306,0.0057</t>
+  </si>
+  <si>
+    <t>0.0507,0.9399,0.0337,0.0034</t>
+  </si>
+  <si>
+    <t>0.5189,0.4240,0.0938,0.0125</t>
+  </si>
+  <si>
+    <t>0.8700,0.1604,0.0126,0.0071</t>
+  </si>
+  <si>
+    <t>0.4422,0.6151,0.0368,0.0300</t>
+  </si>
+  <si>
+    <t>0.8575,0.1552,0.0098,0.0150</t>
+  </si>
+  <si>
+    <t>0.6758,0.4125,0.0151,0.0132</t>
+  </si>
+  <si>
+    <t>0.0080,0.1960,0.9792,0.0032</t>
+  </si>
+  <si>
+    <t>0.8337,0.1635,0.0324,0.0142</t>
+  </si>
+  <si>
+    <t>0.0108,0.0022,0.9915,0.0020</t>
+  </si>
+  <si>
+    <t>0.0323,0.0863,0.9537,0.0038</t>
+  </si>
+  <si>
+    <t>0.0286,0.0451,0.9616,0.0045</t>
+  </si>
+  <si>
+    <t>0.0371,0.5723,0.8587,0.0122</t>
+  </si>
+  <si>
+    <t>0.0654,0.0770,0.9227,0.0113</t>
+  </si>
+  <si>
+    <t>0.0187,0.0043,0.9872,0.0023</t>
+  </si>
+  <si>
+    <t>0.0159,0.0189,0.9812,0.0046</t>
+  </si>
+  <si>
+    <t>0.4524,0.0513,0.5164,0.0067</t>
+  </si>
+  <si>
+    <t>0.3409,0.0663,0.6616,0.0207</t>
+  </si>
+  <si>
+    <t>0.3234,0.4845,0.1918,0.0335</t>
+  </si>
+  <si>
+    <t>0.0268,0.9264,0.1409,0.0042</t>
+  </si>
+  <si>
+    <t>0.0580,0.8280,0.2434,0.0089</t>
+  </si>
+  <si>
+    <t>0.2734,0.5434,0.1855,0.0212</t>
+  </si>
+  <si>
+    <t>0.2168,0.7115,0.1179,0.0313</t>
+  </si>
+  <si>
+    <t>0.4974,0.1571,0.2528,0.0094</t>
+  </si>
+  <si>
+    <t>0.2130,0.8158,0.0362,0.0056</t>
+  </si>
+  <si>
+    <t>0.0532,0.9290,0.0368,0.0045</t>
+  </si>
+  <si>
+    <t>0.2360,0.7658,0.0632,0.0069</t>
+  </si>
+  <si>
+    <t>0.7658,0.3049,0.0119,0.0080</t>
+  </si>
+  <si>
+    <t>0.1482,0.8808,0.0195,0.0050</t>
+  </si>
+  <si>
+    <t>0.0725,0.8911,0.0536,0.0364</t>
+  </si>
+  <si>
+    <t>0.7767,0.0515,0.1942,0.0233</t>
+  </si>
+  <si>
+    <t>0.7952,0.0600,0.1336,0.0497</t>
+  </si>
+  <si>
+    <t>0.5927,0.0766,0.4167,0.0702</t>
+  </si>
+  <si>
+    <t>0.8092,0.0700,0.1355,0.0264</t>
+  </si>
+  <si>
+    <t>0.1677,0.0509,0.8293,0.0466</t>
+  </si>
+  <si>
+    <t>0.1450,0.3821,0.6450,0.0516</t>
+  </si>
+  <si>
+    <t>0.0716,0.5695,0.6227,0.0180</t>
+  </si>
+  <si>
+    <t>0.0888,0.7412,0.4913,0.0261</t>
+  </si>
+  <si>
+    <t>0.0343,0.8543,0.4358,0.0269</t>
+  </si>
+  <si>
+    <t>0.9708,0.0160,0.0022,0.0100</t>
+  </si>
+  <si>
+    <t>0.9858,0.0085,0.0015,0.0036</t>
+  </si>
+  <si>
+    <t>0.9759,0.0132,0.0036,0.0059</t>
+  </si>
+  <si>
+    <t>0.9766,0.0163,0.0042,0.0035</t>
+  </si>
+  <si>
+    <t>0.9420,0.0396,0.0067,0.0141</t>
+  </si>
+  <si>
+    <t>0.9620,0.0230,0.0038,0.0124</t>
+  </si>
+  <si>
+    <t>0.9679,0.0173,0.0036,0.0096</t>
+  </si>
+  <si>
+    <t>0.9338,0.0563,0.0084,0.0118</t>
+  </si>
+  <si>
+    <t>0.0674,0.4019,0.6916,0.0076</t>
+  </si>
+  <si>
+    <t>0.1504,0.7986,0.1087,0.0150</t>
+  </si>
+  <si>
+    <t>0.9097,0.0352,0.0340,0.0301</t>
+  </si>
+  <si>
+    <t>0.0480,0.1678,0.8927,0.0171</t>
+  </si>
+  <si>
+    <t>0.0133,0.0076,0.9715,0.0285</t>
+  </si>
+  <si>
+    <t>0.1292,0.2884,0.6719,0.0258</t>
+  </si>
+  <si>
+    <t>0.0033,0.0164,0.9911,0.0056</t>
+  </si>
+  <si>
+    <t>0.0463,0.5114,0.6762,0.0065</t>
+  </si>
+  <si>
+    <t>0.0259,0.0632,0.9473,0.0359</t>
+  </si>
+  <si>
+    <t>0.1744,0.0871,0.7752,0.0296</t>
+  </si>
+  <si>
+    <t>0.1099,0.6465,0.4158,0.0270</t>
+  </si>
+  <si>
+    <t>0.6838,0.0254,0.3957,0.0133</t>
+  </si>
+  <si>
+    <t>0.5007,0.1998,0.2582,0.0245</t>
+  </si>
+  <si>
+    <t>0.7487,0.0385,0.2707,0.0124</t>
+  </si>
+  <si>
+    <t>0.9505,0.0368,0.0054,0.0097</t>
+  </si>
+  <si>
+    <t>0.9528,0.0540,0.0045,0.0045</t>
+  </si>
+  <si>
+    <t>0.9790,0.0133,0.0028,0.0053</t>
+  </si>
+  <si>
+    <t>0.9466,0.0414,0.0071,0.0108</t>
+  </si>
+  <si>
+    <t>0.9588,0.0387,0.0049,0.0072</t>
+  </si>
+  <si>
+    <t>0.9629,0.0345,0.0035,0.0052</t>
+  </si>
+  <si>
+    <t>0.9625,0.0258,0.0042,0.0073</t>
+  </si>
+  <si>
+    <t>0.9771,0.0114,0.0023,0.0078</t>
+  </si>
+  <si>
+    <t>0.1730,0.3142,0.6064,0.0278</t>
+  </si>
+  <si>
+    <t>0.0178,0.2943,0.9357,0.0143</t>
+  </si>
+  <si>
+    <t>0.0691,0.0430,0.9300,0.0086</t>
+  </si>
+  <si>
+    <t>0.1431,0.2707,0.6133,0.0272</t>
+  </si>
+  <si>
+    <t>0.1641,0.0703,0.7882,0.0696</t>
+  </si>
+  <si>
+    <t>0.2954,0.1058,0.6757,0.1032</t>
+  </si>
+  <si>
+    <t>0.4332,0.0371,0.6450,0.0188</t>
+  </si>
+  <si>
+    <t>0.1131,0.4021,0.6707,0.0516</t>
+  </si>
+  <si>
+    <t>0.6722,0.0605,0.0178,0.3130</t>
+  </si>
+  <si>
+    <t>0.0201,0.3359,0.0127,0.9532</t>
+  </si>
+  <si>
+    <t>0.0381,0.0865,0.0060,0.9619</t>
+  </si>
+  <si>
+    <t>0.0167,0.0066,0.0051,0.9851</t>
+  </si>
+  <si>
+    <t>0.0035,0.0105,0.0011,0.9964</t>
+  </si>
+  <si>
+    <t>0.5829,0.1328,0.0688,0.3349</t>
   </si>
 </sst>
 </file>
@@ -1953,10 +1959,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2127,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2141,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2155,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2169,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2183,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2270,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2281,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2368,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2382,7 @@
         <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,10 +2421,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2438,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2452,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2480,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2491,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2505,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2519,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2536,7 @@
         <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2578,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2631,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2645,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2701,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,10 +2715,10 @@
         <v>259</v>
       </c>
       <c r="C56" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2813,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2858,7 @@
         <v>262</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2911,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2925,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2939,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2970,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2998,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3096,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3107,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3121,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3138,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3152,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3163,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3415,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3429,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3558,7 @@
         <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3597,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3614,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3670,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3698,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3712,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3838,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3849,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3863,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3880,7 @@
         <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3919,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4006,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4034,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4062,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4115,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4160,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4188,7 @@
         <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4202,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4213,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,10 +4227,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4356,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4370,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4384,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4426,7 @@
         <v>262</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,10 +4451,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4535,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4636,7 @@
         <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4650,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4661,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4678,7 @@
         <v>262</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4706,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4720,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4734,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,10 +4745,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4762,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4776,7 @@
         <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4818,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4857,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4871,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4885,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4899,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5042,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5123,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5168,7 @@
         <v>262</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5515,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
